--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F6C5AD-D0B2-4FC3-B90C-AAB2D830FE6D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8F8B5E8-FCBF-432F-9383-F8DF15D8132F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -779,140 +777,26 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -922,8 +806,122 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1329,7 +1327,7 @@
       <c r="AQ1" s="2"/>
     </row>
     <row r="2" spans="1:43" ht="17.399999999999999">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="24" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="14"/>
@@ -1438,8 +1436,8 @@
       <c r="R4" s="11"/>
       <c r="U4" s="20"/>
       <c r="Z4" s="7"/>
-      <c r="AG4" s="58"/>
-      <c r="AH4" s="58"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
       <c r="AI4" s="11"/>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="2"/>
@@ -1496,235 +1494,235 @@
       <c r="AQ5" s="2"/>
     </row>
     <row r="6" spans="1:43" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="53" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="30" t="s">
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="33" t="s">
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="36" t="s">
+      <c r="W6" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="36" t="s">
+      <c r="X6" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="24" t="s">
+      <c r="Y6" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="59" t="s">
+      <c r="Z6" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="53" t="s">
+      <c r="AA6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="53" t="s">
+      <c r="AB6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="43" t="s">
+      <c r="AC6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="45" t="s">
+      <c r="AD6" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="AE6" s="46"/>
-      <c r="AF6" s="47"/>
-      <c r="AG6" s="24" t="s">
+      <c r="AE6" s="55"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="AH6" s="48" t="s">
+      <c r="AH6" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="43" t="s">
+      <c r="AI6" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="55" t="s">
+      <c r="AJ6" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="36" t="s">
+      <c r="AK6" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="53" t="s">
+      <c r="AL6" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="53" t="s">
+      <c r="AM6" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="53" t="s">
+      <c r="AN6" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="53" t="s">
+      <c r="AO6" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="53" t="s">
+      <c r="AP6" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="AQ6" s="24" t="s">
+      <c r="AQ6" s="48" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:43">
-      <c r="A7" s="37"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="68" t="s">
+      <c r="A7" s="34"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="I7" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="27" t="s">
+      <c r="N7" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="66" t="s">
+      <c r="O7" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="67" t="s">
+      <c r="P7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="27" t="s">
+      <c r="R7" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="41" t="s">
+      <c r="S7" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="42"/>
-      <c r="U7" s="39" t="s">
+      <c r="T7" s="70"/>
+      <c r="U7" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="V7" s="34"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="54"/>
-      <c r="AB7" s="54"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="51" t="s">
+      <c r="V7" s="65"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="52"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="52" t="s">
+      <c r="AE7" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="51" t="s">
+      <c r="AF7" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="25"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="56"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="54"/>
-      <c r="AM7" s="54"/>
-      <c r="AN7" s="54"/>
-      <c r="AO7" s="54"/>
-      <c r="AP7" s="54"/>
-      <c r="AQ7" s="25"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="58"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="45"/>
+      <c r="AK7" s="34"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="49"/>
     </row>
     <row r="8" spans="1:43" ht="31.2" customHeight="1" thickBot="1">
-      <c r="A8" s="38"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="57"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
       <c r="S8" s="16" t="s">
         <v>44</v>
       </c>
       <c r="T8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="40"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="61"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="50"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="57"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
-      <c r="AP8" s="29"/>
-      <c r="AQ8" s="26"/>
+      <c r="U8" s="68"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="43"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="43"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="50"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="43"/>
+      <c r="AJ8" s="46"/>
+      <c r="AK8" s="26"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="30"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="30"/>
+      <c r="AP8" s="30"/>
+      <c r="AQ8" s="50"/>
     </row>
     <row r="9" spans="1:43" ht="15" thickTop="1"/>
     <row r="11" spans="1:43">
@@ -1772,70 +1770,38 @@
     </row>
     <row r="14" spans="1:43">
       <c r="B14" s="22"/>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="22"/>
-      <c r="H14" s="69" t="s">
+      <c r="H14" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:43">
       <c r="B15" s="22"/>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="22"/>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
       <c r="L15" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AN6:AN8"/>
     <mergeCell ref="AP6:AP8"/>
     <mergeCell ref="AQ6:AQ8"/>
     <mergeCell ref="I7:I8"/>
@@ -1852,26 +1818,40 @@
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="N7:N8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H15:K15"/>
     <mergeCell ref="O7:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FF280D-8901-47F7-A49B-A58CF91F8AB2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E66AD95-083B-4AB7-B7E6-04F3E141ECAC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8F8B5E8-FCBF-432F-9383-F8DF15D8132F}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14119D01-59AA-428C-BE9D-2271B1D82C47}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>Custodian
 Item
@@ -45,12 +45,6 @@
 Number</t>
   </si>
   <si>
-    <t>Sub-Account</t>
-  </si>
-  <si>
-    <t>Article</t>
-  </si>
-  <si>
     <t>DESCRIPTION</t>
   </si>
   <si>
@@ -230,6 +224,9 @@
   </si>
   <si>
     <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
+  </si>
+  <si>
+    <t>Sub-Account / Article</t>
   </si>
 </sst>
 </file>
@@ -729,13 +726,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -780,23 +774,138 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -806,123 +915,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1242,74 +1239,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AP16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="18" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="18" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="18" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="18" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" style="18" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" style="18" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="18" customWidth="1"/>
-    <col min="11" max="12" width="15" style="18" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" style="18" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="18" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="18"/>
-    <col min="16" max="16" width="14.6640625" style="18" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="18" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" style="18" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" style="18" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" style="18"/>
-    <col min="22" max="22" width="12.44140625" style="18" customWidth="1"/>
-    <col min="23" max="24" width="8.88671875" style="18"/>
-    <col min="25" max="25" width="13.44140625" style="18" customWidth="1"/>
-    <col min="26" max="26" width="11.21875" style="18" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" style="18" customWidth="1"/>
-    <col min="28" max="28" width="13.77734375" style="18" customWidth="1"/>
-    <col min="29" max="29" width="11.109375" style="18" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" style="18" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" style="18" customWidth="1"/>
-    <col min="32" max="32" width="19.21875" style="18" customWidth="1"/>
-    <col min="33" max="33" width="22.88671875" style="18" customWidth="1"/>
-    <col min="34" max="40" width="8.88671875" style="18"/>
-    <col min="41" max="41" width="11.109375" style="18" customWidth="1"/>
-    <col min="42" max="42" width="11" style="18" customWidth="1"/>
-    <col min="43" max="16384" width="8.88671875" style="18"/>
+    <col min="1" max="1" width="13.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" style="17" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="17" customWidth="1"/>
+    <col min="10" max="11" width="15" style="17" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="17" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" style="17" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="17"/>
+    <col min="15" max="15" width="14.6640625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="17" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" style="17" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" style="17" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="17"/>
+    <col min="21" max="21" width="12.44140625" style="17" customWidth="1"/>
+    <col min="22" max="23" width="8.88671875" style="17"/>
+    <col min="24" max="24" width="13.44140625" style="17" customWidth="1"/>
+    <col min="25" max="25" width="11.21875" style="17" customWidth="1"/>
+    <col min="26" max="26" width="11.5546875" style="17" customWidth="1"/>
+    <col min="27" max="27" width="13.77734375" style="17" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="17" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" style="17" customWidth="1"/>
+    <col min="30" max="30" width="14.33203125" style="17" customWidth="1"/>
+    <col min="31" max="31" width="19.21875" style="17" customWidth="1"/>
+    <col min="32" max="32" width="22.88671875" style="17" customWidth="1"/>
+    <col min="33" max="39" width="8.88671875" style="17"/>
+    <col min="40" max="40" width="11.109375" style="17" customWidth="1"/>
+    <col min="41" max="41" width="11" style="17" customWidth="1"/>
+    <col min="42" max="16384" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="20.399999999999999" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="14"/>
+    <row r="1" spans="1:42" ht="20.399999999999999" customHeight="1">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="8"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="2"/>
       <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="5"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
       <c r="Y1" s="5"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
       <c r="AE1" s="2"/>
@@ -1324,38 +1320,37 @@
       <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
     </row>
-    <row r="2" spans="1:43" ht="17.399999999999999">
-      <c r="A2" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="14"/>
+    <row r="2" spans="1:42" ht="17.399999999999999">
+      <c r="A2" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="13"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="8"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="2"/>
       <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="5"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
       <c r="Y2" s="5"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
@@ -1370,36 +1365,35 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
     </row>
-    <row r="3" spans="1:43">
-      <c r="A3" s="4"/>
+    <row r="3" spans="1:42">
+      <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="H3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="8"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="5"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
       <c r="Y3" s="5"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
@@ -1414,443 +1408,471 @@
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
     </row>
-    <row r="4" spans="1:43" ht="15.6">
-      <c r="A4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="U4" s="20"/>
-      <c r="Z4" s="7"/>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
+    <row r="4" spans="1:42">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
     </row>
-    <row r="5" spans="1:43" ht="15" thickBot="1">
-      <c r="A5" s="2"/>
+    <row r="5" spans="1:42" ht="15.6">
+      <c r="A5" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
       <c r="I5" s="10"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="T5" s="19"/>
+      <c r="Y5" s="6"/>
+      <c r="AF5" s="53"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
       <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
     </row>
-    <row r="6" spans="1:43" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="33" t="s">
+    <row r="6" spans="1:42" ht="15" thickBot="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="10"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+    </row>
+    <row r="7" spans="1:42" ht="15" customHeight="1" thickTop="1">
+      <c r="A7" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="39" t="s">
+      <c r="B7" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E7" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="63"/>
-      <c r="P6" s="61" t="s">
+      <c r="V7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="63"/>
-      <c r="V6" s="64" t="s">
+      <c r="W7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="33" t="s">
+      <c r="X7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="33" t="s">
+      <c r="Y7" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="48" t="s">
+      <c r="Z7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="51" t="s">
+      <c r="AA7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="39" t="s">
+      <c r="AB7" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="39" t="s">
+      <c r="AC7" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="41" t="s">
+      <c r="AD7" s="58"/>
+      <c r="AE7" s="59"/>
+      <c r="AF7" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG7" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="54" t="s">
+      <c r="AH7" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="AE6" s="55"/>
-      <c r="AF6" s="56"/>
-      <c r="AG6" s="48" t="s">
+      <c r="AI7" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ7" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM7" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN7" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP7" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42">
+      <c r="A8" s="40"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="R8" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" s="45"/>
+      <c r="T8" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" s="37"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="55"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="47"/>
+      <c r="AC8" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD8" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE8" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="61"/>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="51"/>
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="26"/>
+      <c r="AL8" s="26"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="26"/>
+      <c r="AP8" s="29"/>
+    </row>
+    <row r="9" spans="1:42" ht="48" customHeight="1" thickBot="1">
+      <c r="A9" s="41"/>
+      <c r="B9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="T9" s="43"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="32"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="41"/>
+      <c r="AK9" s="27"/>
+      <c r="AL9" s="27"/>
+      <c r="AM9" s="27"/>
+      <c r="AN9" s="27"/>
+      <c r="AO9" s="27"/>
+      <c r="AP9" s="30"/>
+    </row>
+    <row r="10" spans="1:42" ht="15" thickTop="1">
+      <c r="Y10" s="24"/>
+    </row>
+    <row r="12" spans="1:42">
+      <c r="B12" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="AH6" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI6" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ6" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK6" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL6" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM6" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN6" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO6" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="AP6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="AQ6" s="48" t="s">
-        <v>24</v>
-      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="G12" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
     </row>
-    <row r="7" spans="1:43">
-      <c r="A7" s="34"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q7" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" s="70"/>
-      <c r="U7" s="67" t="s">
-        <v>38</v>
-      </c>
-      <c r="V7" s="65"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="40"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE7" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF7" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="58"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="45"/>
-      <c r="AK7" s="34"/>
-      <c r="AL7" s="40"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="49"/>
+    <row r="13" spans="1:42">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
     </row>
-    <row r="8" spans="1:43" ht="31.2" customHeight="1" thickBot="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="68"/>
-      <c r="V8" s="66"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="43"/>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="43"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="28"/>
-      <c r="AI8" s="43"/>
-      <c r="AJ8" s="46"/>
-      <c r="AK8" s="26"/>
-      <c r="AL8" s="30"/>
-      <c r="AM8" s="30"/>
-      <c r="AN8" s="30"/>
-      <c r="AO8" s="30"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="50"/>
+    <row r="14" spans="1:42">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
     </row>
-    <row r="9" spans="1:43" ht="15" thickTop="1"/>
-    <row r="11" spans="1:43">
-      <c r="B11" s="21" t="s">
+    <row r="15" spans="1:42">
+      <c r="B15" s="21"/>
+      <c r="C15" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="H15" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+    </row>
+    <row r="16" spans="1:42">
+      <c r="B16" s="21"/>
+      <c r="C16" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:43">
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-    </row>
-    <row r="13" spans="1:43">
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="22"/>
-    </row>
-    <row r="14" spans="1:43">
-      <c r="B14" s="22"/>
-      <c r="C14" s="31" t="s">
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="H16" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="22"/>
-      <c r="H14" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="22"/>
-    </row>
-    <row r="15" spans="1:43">
-      <c r="B15" s="22"/>
-      <c r="C15" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="22"/>
-      <c r="H15" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="22"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="AP6:AP8"/>
-    <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="G6:O6"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="C14:E14"/>
+  <mergeCells count="48">
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="N8:N9"/>
     <mergeCell ref="H15:K15"/>
-    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AP7:AP9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="F7:N7"/>
+    <mergeCell ref="O7:T7"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M8:M9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14119D01-59AA-428C-BE9D-2271B1D82C47}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B924738-7D39-472C-A1CD-4AA391BE52BB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -774,7 +774,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -857,6 +857,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -887,18 +899,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -918,8 +918,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1471,8 +1475,8 @@
       <c r="Q5" s="10"/>
       <c r="T5" s="19"/>
       <c r="Y5" s="6"/>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
+      <c r="AF5" s="57"/>
+      <c r="AG5" s="57"/>
       <c r="AH5" s="10"/>
       <c r="AI5" s="10"/>
       <c r="AJ5" s="2"/>
@@ -1531,10 +1535,10 @@
       <c r="A7" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="64"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="25" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1576,7 @@
       <c r="X7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="Y7" s="54" t="s">
+      <c r="Y7" s="58" t="s">
         <v>8</v>
       </c>
       <c r="Z7" s="25" t="s">
@@ -1584,15 +1588,15 @@
       <c r="AB7" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="AC7" s="57" t="s">
+      <c r="AC7" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AD7" s="58"/>
-      <c r="AE7" s="59"/>
+      <c r="AD7" s="62"/>
+      <c r="AE7" s="63"/>
       <c r="AF7" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="AG7" s="60" t="s">
+      <c r="AG7" s="64" t="s">
         <v>13</v>
       </c>
       <c r="AH7" s="46" t="s">
@@ -1625,8 +1629,8 @@
     </row>
     <row r="8" spans="1:42">
       <c r="A8" s="40"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="66"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="26"/>
       <c r="E8" s="47"/>
       <c r="F8" s="68" t="s">
@@ -1676,7 +1680,7 @@
       <c r="V8" s="40"/>
       <c r="W8" s="40"/>
       <c r="X8" s="29"/>
-      <c r="Y8" s="55"/>
+      <c r="Y8" s="59"/>
       <c r="Z8" s="26"/>
       <c r="AA8" s="26"/>
       <c r="AB8" s="47"/>
@@ -1690,7 +1694,7 @@
         <v>39</v>
       </c>
       <c r="AF8" s="29"/>
-      <c r="AG8" s="61"/>
+      <c r="AG8" s="65"/>
       <c r="AH8" s="47"/>
       <c r="AI8" s="51"/>
       <c r="AJ8" s="40"/>
@@ -1711,7 +1715,7 @@
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="32"/>
-      <c r="F9" s="62"/>
+      <c r="F9" s="66"/>
       <c r="G9" s="27"/>
       <c r="H9" s="32"/>
       <c r="I9" s="27"/>
@@ -1734,7 +1738,7 @@
       <c r="V9" s="41"/>
       <c r="W9" s="41"/>
       <c r="X9" s="30"/>
-      <c r="Y9" s="56"/>
+      <c r="Y9" s="60"/>
       <c r="Z9" s="27"/>
       <c r="AA9" s="27"/>
       <c r="AB9" s="32"/>
@@ -1742,7 +1746,7 @@
       <c r="AD9" s="32"/>
       <c r="AE9" s="27"/>
       <c r="AF9" s="30"/>
-      <c r="AG9" s="62"/>
+      <c r="AG9" s="66"/>
       <c r="AH9" s="32"/>
       <c r="AI9" s="52"/>
       <c r="AJ9" s="41"/>
@@ -1754,7 +1758,92 @@
       <c r="AP9" s="30"/>
     </row>
     <row r="10" spans="1:42" ht="15" thickTop="1">
-      <c r="Y10" s="24"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="72"/>
+      <c r="AB10" s="72"/>
+      <c r="AC10" s="72"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="72"/>
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="72"/>
+      <c r="AL10" s="72"/>
+      <c r="AM10" s="72"/>
+      <c r="AN10" s="72"/>
+      <c r="AO10" s="72"/>
+      <c r="AP10" s="72"/>
+    </row>
+    <row r="11" spans="1:42">
+      <c r="A11" s="72"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="72"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="72"/>
+      <c r="Y11" s="72"/>
+      <c r="Z11" s="72"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="72"/>
+      <c r="AC11" s="72"/>
+      <c r="AD11" s="72"/>
+      <c r="AE11" s="72"/>
+      <c r="AF11" s="72"/>
+      <c r="AG11" s="72"/>
+      <c r="AH11" s="72"/>
+      <c r="AI11" s="72"/>
+      <c r="AJ11" s="72"/>
+      <c r="AK11" s="72"/>
+      <c r="AL11" s="72"/>
+      <c r="AM11" s="72"/>
+      <c r="AN11" s="72"/>
+      <c r="AO11" s="72"/>
+      <c r="AP11" s="72"/>
     </row>
     <row r="12" spans="1:42">
       <c r="B12" s="20" t="s">
@@ -1789,8 +1878,7 @@
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="73"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
@@ -1825,9 +1913,6 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="L8:L9"/>
@@ -1847,6 +1932,9 @@
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AF7:AF9"/>
     <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
     <mergeCell ref="AH7:AH9"/>
     <mergeCell ref="AC8:AC9"/>
     <mergeCell ref="AD8:AD9"/>

--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B924738-7D39-472C-A1CD-4AA391BE52BB}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36196CFD-B31A-4DF3-BD20-E77466A967EA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Custodian
 Item
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Set/Lot #</t>
-  </si>
-  <si>
-    <t>Sub-Article</t>
   </si>
   <si>
     <t>Make / 
@@ -325,7 +322,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -719,6 +716,19 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -775,137 +785,11 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -915,14 +799,140 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1243,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AP16"/>
+  <dimension ref="A1:AO16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="17" customWidth="1"/>
@@ -1251,64 +1261,64 @@
     <col min="3" max="3" width="13.6640625" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" style="17" customWidth="1"/>
     <col min="5" max="5" width="33.109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" style="17" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="17" customWidth="1"/>
-    <col min="10" max="11" width="15" style="17" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="17" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" style="17" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="17"/>
-    <col min="15" max="15" width="14.6640625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="17" customWidth="1"/>
-    <col min="17" max="17" width="17.33203125" style="17" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" style="17" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="17"/>
-    <col min="21" max="21" width="12.44140625" style="17" customWidth="1"/>
-    <col min="22" max="23" width="8.88671875" style="17"/>
-    <col min="24" max="24" width="13.44140625" style="17" customWidth="1"/>
-    <col min="25" max="25" width="11.21875" style="17" customWidth="1"/>
-    <col min="26" max="26" width="11.5546875" style="17" customWidth="1"/>
-    <col min="27" max="27" width="13.77734375" style="17" customWidth="1"/>
-    <col min="28" max="28" width="11.109375" style="17" customWidth="1"/>
-    <col min="29" max="29" width="13.44140625" style="17" customWidth="1"/>
-    <col min="30" max="30" width="14.33203125" style="17" customWidth="1"/>
-    <col min="31" max="31" width="19.21875" style="17" customWidth="1"/>
-    <col min="32" max="32" width="22.88671875" style="17" customWidth="1"/>
-    <col min="33" max="39" width="8.88671875" style="17"/>
-    <col min="40" max="40" width="11.109375" style="17" customWidth="1"/>
-    <col min="41" max="41" width="11" style="17" customWidth="1"/>
-    <col min="42" max="16384" width="8.88671875" style="17"/>
+    <col min="6" max="6" width="9.77734375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="17" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="17" customWidth="1"/>
+    <col min="9" max="10" width="15" style="17" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="17" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="17" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" style="17"/>
+    <col min="14" max="14" width="14.6640625" style="17" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="17" customWidth="1"/>
+    <col min="17" max="17" width="11.5546875" style="17" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="17"/>
+    <col min="20" max="20" width="12.44140625" style="17" customWidth="1"/>
+    <col min="21" max="22" width="8.88671875" style="17"/>
+    <col min="23" max="23" width="13.44140625" style="17" customWidth="1"/>
+    <col min="24" max="24" width="11.21875" style="17" customWidth="1"/>
+    <col min="25" max="25" width="11.5546875" style="17" customWidth="1"/>
+    <col min="26" max="26" width="13.77734375" style="17" customWidth="1"/>
+    <col min="27" max="27" width="11.109375" style="17" customWidth="1"/>
+    <col min="28" max="28" width="13.44140625" style="17" customWidth="1"/>
+    <col min="29" max="29" width="14.33203125" style="17" customWidth="1"/>
+    <col min="30" max="30" width="19.21875" style="17" customWidth="1"/>
+    <col min="31" max="31" width="22.88671875" style="17" customWidth="1"/>
+    <col min="32" max="38" width="8.88671875" style="17"/>
+    <col min="39" max="39" width="11.109375" style="17" customWidth="1"/>
+    <col min="40" max="40" width="11" style="17" customWidth="1"/>
+    <col min="41" max="16384" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:41" ht="20.399999999999999" customHeight="1">
       <c r="A1" s="12"/>
       <c r="B1" s="13"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="2"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="2"/>
       <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
+      <c r="V1" s="4"/>
       <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
+      <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -1323,37 +1333,37 @@
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
     </row>
-    <row r="2" spans="1:42" ht="17.399999999999999">
+    <row r="2" spans="1:41" ht="17.399999999999999">
       <c r="A2" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="2"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -1368,35 +1378,35 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:41">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="2"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="2"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="V3" s="4"/>
       <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
@@ -1411,35 +1421,35 @@
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:41">
       <c r="A4" s="3"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="2"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
+      <c r="V4" s="4"/>
       <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
@@ -1454,40 +1464,38 @@
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
     </row>
-    <row r="5" spans="1:42" ht="15.6">
+    <row r="5" spans="1:41" ht="15.6">
       <c r="A5" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="18"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
       <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="T5" s="19"/>
-      <c r="Y5" s="6"/>
-      <c r="AF5" s="57"/>
-      <c r="AG5" s="57"/>
+      <c r="S5" s="19"/>
+      <c r="X5" s="6"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="10"/>
       <c r="AH5" s="10"/>
-      <c r="AI5" s="10"/>
+      <c r="AI5" s="2"/>
       <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
     </row>
-    <row r="6" spans="1:42" ht="15" thickBot="1">
+    <row r="6" spans="1:41" ht="15" thickBot="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1495,372 +1503,363 @@
       <c r="E6" s="2"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="2"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="10"/>
       <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
+      <c r="AE6" s="11"/>
       <c r="AF6" s="11"/>
-      <c r="AG6" s="11"/>
+      <c r="AG6" s="10"/>
       <c r="AH6" s="10"/>
-      <c r="AI6" s="10"/>
+      <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
       <c r="AK6" s="2"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
     </row>
-    <row r="7" spans="1:42" ht="15" customHeight="1" thickTop="1">
-      <c r="A7" s="39" t="s">
+    <row r="7" spans="1:41" ht="15" customHeight="1" thickTop="1">
+      <c r="A7" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="37"/>
+      <c r="D7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="U7" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="X7" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB7" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC7" s="53"/>
+      <c r="AD7" s="54"/>
+      <c r="AE7" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="V7" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="W7" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="X7" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y7" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC7" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD7" s="62"/>
-      <c r="AE7" s="63"/>
-      <c r="AF7" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG7" s="64" t="s">
+      <c r="AF7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="AH7" s="46" t="s">
+      <c r="AG7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="AI7" s="50" t="s">
+      <c r="AH7" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="AJ7" s="39" t="s">
+      <c r="AI7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="AK7" s="25" t="s">
+      <c r="AJ7" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="AL7" s="25" t="s">
+      <c r="AK7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="AM7" s="25" t="s">
+      <c r="AL7" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AN7" s="25" t="s">
+      <c r="AM7" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="AO7" s="25" t="s">
+      <c r="AN7" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AP7" s="28" t="s">
+      <c r="AO7" s="46" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:42">
-      <c r="A8" s="40"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="68" t="s">
+    <row r="8" spans="1:41">
+      <c r="A8" s="34"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K8" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L8" s="29" t="s">
         <v>29</v>
       </c>
       <c r="M8" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="N8" s="71" t="s">
+      <c r="N8" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="67" t="s">
+      <c r="O8" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="P8" s="31" t="s">
+      <c r="P8" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="Q8" s="31" t="s">
+      <c r="Q8" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="R8" s="44" t="s">
+      <c r="R8" s="72"/>
+      <c r="S8" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="S8" s="45"/>
-      <c r="T8" s="42" t="s">
+      <c r="T8" s="67"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="47"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="41"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="U8" s="37"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="59"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="47"/>
-      <c r="AC8" s="48" t="s">
+      <c r="AC8" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="AD8" s="49" t="s">
+      <c r="AD8" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="AE8" s="48" t="s">
+      <c r="AE8" s="47"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="43"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="41"/>
+      <c r="AL8" s="41"/>
+      <c r="AM8" s="41"/>
+      <c r="AN8" s="41"/>
+      <c r="AO8" s="47"/>
+    </row>
+    <row r="9" spans="1:41" ht="48" customHeight="1" thickBot="1">
+      <c r="A9" s="35"/>
+      <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="65"/>
-      <c r="AH8" s="47"/>
-      <c r="AI8" s="51"/>
-      <c r="AJ8" s="40"/>
-      <c r="AK8" s="26"/>
-      <c r="AL8" s="26"/>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="26"/>
-      <c r="AP8" s="29"/>
+      <c r="C9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="S9" s="70"/>
+      <c r="T9" s="68"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="57"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="32"/>
+      <c r="AI9" s="35"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="48"/>
     </row>
-    <row r="9" spans="1:42" ht="48" customHeight="1" thickBot="1">
-      <c r="A9" s="41"/>
-      <c r="B9" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="S9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T9" s="43"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="66"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="30"/>
+    <row r="10" spans="1:41" ht="15" thickTop="1">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="25"/>
+      <c r="AM10" s="25"/>
+      <c r="AN10" s="25"/>
+      <c r="AO10" s="25"/>
     </row>
-    <row r="10" spans="1:42" ht="15" thickTop="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="73"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="72"/>
-      <c r="AB10" s="72"/>
-      <c r="AC10" s="72"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="72"/>
-      <c r="AJ10" s="72"/>
-      <c r="AK10" s="72"/>
-      <c r="AL10" s="72"/>
-      <c r="AM10" s="72"/>
-      <c r="AN10" s="72"/>
-      <c r="AO10" s="72"/>
-      <c r="AP10" s="72"/>
+    <row r="11" spans="1:41">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+      <c r="AK11" s="25"/>
+      <c r="AL11" s="25"/>
+      <c r="AM11" s="25"/>
+      <c r="AN11" s="25"/>
+      <c r="AO11" s="25"/>
     </row>
-    <row r="11" spans="1:42">
-      <c r="A11" s="72"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="72"/>
-      <c r="AB11" s="72"/>
-      <c r="AC11" s="72"/>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="72"/>
-      <c r="AF11" s="72"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="72"/>
-      <c r="AI11" s="72"/>
-      <c r="AJ11" s="72"/>
-      <c r="AK11" s="72"/>
-      <c r="AL11" s="72"/>
-      <c r="AM11" s="72"/>
-      <c r="AN11" s="72"/>
-      <c r="AO11" s="72"/>
-      <c r="AP11" s="72"/>
-    </row>
-    <row r="12" spans="1:42">
+    <row r="12" spans="1:41">
       <c r="B12" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
       <c r="G12" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
     </row>
-    <row r="13" spans="1:42">
+    <row r="13" spans="1:41">
       <c r="B13" s="20"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
@@ -1870,95 +1869,92 @@
       <c r="H13" s="21"/>
       <c r="I13" s="21"/>
       <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
     </row>
-    <row r="14" spans="1:42">
+    <row r="14" spans="1:41">
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
-      <c r="F14" s="21"/>
       <c r="H14" s="24"/>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:42">
+    <row r="15" spans="1:41">
       <c r="B15" s="21"/>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="H15" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="1:41">
+      <c r="B16" s="21"/>
+      <c r="C16" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="H15" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-    </row>
-    <row r="16" spans="1:42">
-      <c r="B16" s="21"/>
-      <c r="C16" s="70" t="s">
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="H16" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="H16" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="N8:N9"/>
+  <mergeCells count="47">
+    <mergeCell ref="F7:M7"/>
     <mergeCell ref="H15:K15"/>
     <mergeCell ref="H16:K16"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AL7:AL9"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:C8"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
-    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="W7:W9"/>
     <mergeCell ref="X7:X9"/>
     <mergeCell ref="Y7:Y9"/>
     <mergeCell ref="Z7:Z9"/>
     <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="AB7:AD7"/>
+    <mergeCell ref="AE7:AE9"/>
     <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="N8:N9"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AP7:AP9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F7:N7"/>
-    <mergeCell ref="O7:T7"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="M8:M9"/>
   </mergeCells>

--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36196CFD-B31A-4DF3-BD20-E77466A967EA}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{8BFCFD28-C360-4725-B32A-0C5023D6DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22B122B4-A799-434D-B892-F083F0293ACA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -322,7 +322,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -726,6 +726,15 @@
       <top style="thick">
         <color indexed="64"/>
       </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="hair">
         <color indexed="64"/>
       </bottom>
@@ -736,7 +745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -788,8 +797,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -799,27 +817,84 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -830,35 +905,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -889,50 +940,23 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -950,10 +974,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1253,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AO17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="17" customWidth="1"/>
@@ -1483,8 +1503,8 @@
       <c r="P5" s="10"/>
       <c r="S5" s="19"/>
       <c r="X5" s="6"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
+      <c r="AE5" s="62"/>
+      <c r="AF5" s="62"/>
       <c r="AG5" s="10"/>
       <c r="AH5" s="10"/>
       <c r="AI5" s="2"/>
@@ -1539,405 +1559,424 @@
       <c r="AO6" s="2"/>
     </row>
     <row r="7" spans="1:41" ht="15" customHeight="1" thickTop="1">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="40" t="s">
+      <c r="C7" s="59"/>
+      <c r="D7" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="63" t="s">
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="66" t="s">
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="U7" s="33" t="s">
+      <c r="U7" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="V7" s="33" t="s">
+      <c r="V7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="W7" s="46" t="s">
+      <c r="W7" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="X7" s="49" t="s">
+      <c r="X7" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="40" t="s">
+      <c r="Y7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="Z7" s="40" t="s">
+      <c r="Z7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AA7" s="42" t="s">
+      <c r="AA7" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="AB7" s="52" t="s">
+      <c r="AB7" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="54"/>
-      <c r="AE7" s="46" t="s">
+      <c r="AC7" s="67"/>
+      <c r="AD7" s="68"/>
+      <c r="AE7" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AF7" s="55" t="s">
+      <c r="AF7" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AG7" s="42" t="s">
+      <c r="AG7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AH7" s="61" t="s">
+      <c r="AH7" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="AI7" s="33" t="s">
+      <c r="AI7" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="AJ7" s="40" t="s">
+      <c r="AJ7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AK7" s="40" t="s">
+      <c r="AK7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="AL7" s="40" t="s">
+      <c r="AL7" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AM7" s="40" t="s">
+      <c r="AM7" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AN7" s="40" t="s">
+      <c r="AN7" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AO7" s="46" t="s">
+      <c r="AO7" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:41">
-      <c r="A8" s="34"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="29" t="s">
+      <c r="A8" s="45"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="M8" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="N8" s="58" t="s">
+      <c r="N8" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="29" t="s">
+      <c r="O8" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="P8" s="29" t="s">
+      <c r="P8" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="Q8" s="71" t="s">
+      <c r="Q8" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="R8" s="72"/>
-      <c r="S8" s="69" t="s">
+      <c r="R8" s="50"/>
+      <c r="S8" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="T8" s="67"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="47"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="41"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="43"/>
-      <c r="AB8" s="59" t="s">
+      <c r="T8" s="42"/>
+      <c r="U8" s="45"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="AC8" s="60" t="s">
+      <c r="AC8" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="AD8" s="59" t="s">
+      <c r="AD8" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="AE8" s="47"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="43"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="41"/>
-      <c r="AK8" s="41"/>
-      <c r="AL8" s="41"/>
-      <c r="AM8" s="41"/>
-      <c r="AN8" s="41"/>
-      <c r="AO8" s="47"/>
+      <c r="AE8" s="36"/>
+      <c r="AF8" s="70"/>
+      <c r="AG8" s="52"/>
+      <c r="AH8" s="56"/>
+      <c r="AI8" s="45"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="36"/>
     </row>
     <row r="9" spans="1:41" ht="48" customHeight="1" thickBot="1">
-      <c r="A9" s="35"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
       <c r="Q9" s="15" t="s">
         <v>41</v>
       </c>
       <c r="R9" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="S9" s="70"/>
-      <c r="T9" s="68"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="30"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="57"/>
-      <c r="AG9" s="44"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="30"/>
-      <c r="AK9" s="30"/>
-      <c r="AL9" s="30"/>
-      <c r="AM9" s="30"/>
-      <c r="AN9" s="30"/>
-      <c r="AO9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="39"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="34"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="39"/>
+      <c r="AH9" s="57"/>
+      <c r="AI9" s="46"/>
+      <c r="AJ9" s="34"/>
+      <c r="AK9" s="34"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="34"/>
+      <c r="AN9" s="34"/>
+      <c r="AO9" s="37"/>
     </row>
-    <row r="10" spans="1:41" ht="15" thickTop="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="25"/>
-      <c r="AI10" s="25"/>
-      <c r="AJ10" s="25"/>
-      <c r="AK10" s="25"/>
-      <c r="AL10" s="25"/>
-      <c r="AM10" s="25"/>
-      <c r="AN10" s="25"/>
-      <c r="AO10" s="25"/>
+    <row r="10" spans="1:41" ht="48" hidden="1" customHeight="1" thickTop="1">
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="77"/>
+      <c r="T10" s="76"/>
+      <c r="U10" s="76"/>
+      <c r="V10" s="76"/>
+      <c r="W10" s="76"/>
+      <c r="X10" s="78"/>
+      <c r="Y10" s="76"/>
+      <c r="Z10" s="76"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="76"/>
+      <c r="AC10" s="26"/>
+      <c r="AD10" s="76"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="76"/>
+      <c r="AJ10" s="76"/>
+      <c r="AK10" s="76"/>
+      <c r="AL10" s="76"/>
+      <c r="AM10" s="76"/>
+      <c r="AN10" s="76"/>
+      <c r="AO10" s="76"/>
     </row>
-    <row r="11" spans="1:41">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="25"/>
-      <c r="AJ11" s="25"/>
-      <c r="AK11" s="25"/>
-      <c r="AL11" s="25"/>
-      <c r="AM11" s="25"/>
-      <c r="AN11" s="25"/>
-      <c r="AO11" s="25"/>
+    <row r="11" spans="1:41" ht="15" thickTop="1">
+      <c r="A11" s="74"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
+      <c r="S11" s="74"/>
+      <c r="T11" s="74"/>
+      <c r="U11" s="74"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="74"/>
+      <c r="X11" s="75"/>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="74"/>
+      <c r="AA11" s="74"/>
+      <c r="AB11" s="74"/>
+      <c r="AC11" s="74"/>
+      <c r="AD11" s="74"/>
+      <c r="AE11" s="74"/>
+      <c r="AF11" s="74"/>
+      <c r="AG11" s="74"/>
+      <c r="AH11" s="74"/>
+      <c r="AI11" s="74"/>
+      <c r="AJ11" s="74"/>
+      <c r="AK11" s="74"/>
+      <c r="AL11" s="74"/>
+      <c r="AM11" s="74"/>
+      <c r="AN11" s="74"/>
+      <c r="AO11" s="74"/>
     </row>
     <row r="12" spans="1:41">
-      <c r="B12" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="G12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="25"/>
+      <c r="AK12" s="25"/>
+      <c r="AL12" s="25"/>
+      <c r="AM12" s="25"/>
+      <c r="AN12" s="25"/>
+      <c r="AO12" s="25"/>
     </row>
     <row r="13" spans="1:41">
-      <c r="B13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>46</v>
+      </c>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="G13" s="21" t="s">
+        <v>50</v>
+      </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21"/>
       <c r="J13" s="21"/>
     </row>
     <row r="14" spans="1:41">
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
     </row>
     <row r="15" spans="1:41">
       <c r="B15" s="21"/>
-      <c r="C15" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="H15" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" spans="1:41">
       <c r="B16" s="21"/>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="H16" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="21"/>
+      <c r="C17" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="H16" s="28" t="s">
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="H17" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="T7:T9"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M8:M9"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:C8"/>
     <mergeCell ref="D7:D9"/>
@@ -1953,10 +1992,34 @@
     <mergeCell ref="AF7:AF9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:R8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_14/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_22/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{FD76107A-A50E-4211-B2F4-EE95EDB93CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D07AFD-2025-40F4-ADA6-D25C7B890F75}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{FD76107A-A50E-4211-B2F4-EE95EDB93CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7346B3-CA4B-4113-BA38-32B7620E4FF6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Custodian 
 Item 
@@ -75,12 +75,6 @@
 Number</t>
   </si>
   <si>
-    <t>Old
-Amounts
-(recorded 
-in RPCPPE)</t>
-  </si>
-  <si>
     <t>P.O. 
 Date</t>
   </si>
@@ -235,32 +229,25 @@
 Number</t>
   </si>
   <si>
-    <t>Certified Correct by:</t>
-  </si>
-  <si>
-    <t>Signature over Printed Name</t>
-  </si>
-  <si>
-    <t>Custodian</t>
-  </si>
-  <si>
-    <t>Verified by:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Assistant to the Custodian</t>
-  </si>
-  <si>
     <t>Department:</t>
   </si>
   <si>
     <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
+  </si>
+  <si>
+    <t>Old
+Amounts
+(in RPCPPE)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,10 +296,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri  "/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,14 +315,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -475,38 +459,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -524,14 +482,34 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -541,43 +519,27 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -894,8 +856,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C18FA19-E183-4684-9A16-B0E4B19C4ED4}">
-  <dimension ref="B2:AU19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B2:AU14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -911,16 +873,19 @@
     <col min="16" max="19" width="8.88671875" style="3"/>
     <col min="20" max="20" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.21875" style="3" customWidth="1"/>
     <col min="23" max="23" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.88671875" style="3"/>
-    <col min="25" max="25" width="10.5546875" style="3" customWidth="1"/>
-    <col min="26" max="28" width="8.88671875" style="3"/>
-    <col min="29" max="29" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" style="3" customWidth="1"/>
-    <col min="31" max="31" width="11.33203125" style="3" customWidth="1"/>
-    <col min="32" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="10.88671875" style="3" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" style="24" customWidth="1"/>
+    <col min="26" max="26" width="11.44140625" style="3" customWidth="1"/>
+    <col min="27" max="28" width="8.88671875" style="3"/>
+    <col min="29" max="29" width="13" style="3" customWidth="1"/>
+    <col min="30" max="30" width="11.44140625" style="24" customWidth="1"/>
+    <col min="31" max="31" width="12.109375" style="24" customWidth="1"/>
+    <col min="32" max="32" width="12.21875" style="24" customWidth="1"/>
+    <col min="33" max="33" width="11.6640625" style="3" customWidth="1"/>
+    <col min="34" max="35" width="8.88671875" style="3"/>
+    <col min="36" max="36" width="10.88671875" style="24" customWidth="1"/>
     <col min="37" max="38" width="8.88671875" style="3"/>
     <col min="39" max="39" width="13.6640625" style="3" customWidth="1"/>
     <col min="40" max="41" width="8.88671875" style="3"/>
@@ -932,422 +897,347 @@
     <col min="47" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:47" s="1" customFormat="1" ht="15.6">
+    <row r="2" spans="2:47" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
+      <c r="Y2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AJ2" s="22"/>
     </row>
-    <row r="3" spans="2:47" s="2" customFormat="1" ht="18">
+    <row r="3" spans="2:47" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>57</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="Y3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AJ3" s="23"/>
     </row>
-    <row r="4" spans="2:47" ht="15.6">
+    <row r="4" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="2:47" ht="15.6">
+    <row r="5" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="2:47" ht="15.6">
-      <c r="B6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="12"/>
+    <row r="6" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="2:47" ht="15" thickBot="1"/>
-    <row r="8" spans="2:47" s="4" customFormat="1">
-      <c r="B8" s="14" t="s">
+    <row r="7" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="2:47" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="20" t="s">
+      <c r="D12" s="15"/>
+      <c r="E12" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F12" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17" t="s">
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD12" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="15"/>
+      <c r="AR12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU12" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:47" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="20"/>
+      <c r="C13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="X8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB8" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD8" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF8" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG8" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ8" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AL8" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM8" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="AN8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="AO8" s="17" t="s">
+      <c r="Q13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="11"/>
+      <c r="AI13" s="11"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="11"/>
+      <c r="AL13" s="11"/>
+      <c r="AM13" s="11"/>
+      <c r="AN13" s="11"/>
+      <c r="AO13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="17"/>
-      <c r="AR8" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="AS8" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="AT8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AU8" s="23" t="s">
-        <v>31</v>
-      </c>
+      <c r="AP13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ13" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="11"/>
+      <c r="AT13" s="11"/>
+      <c r="AU13" s="17"/>
     </row>
-    <row r="9" spans="2:47" s="4" customFormat="1">
-      <c r="B9" s="15"/>
-      <c r="C9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="R9" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="S9" s="18" t="s">
+    <row r="14" spans="2:47" s="4" customFormat="1" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="21"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="T9" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="18"/>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="21"/>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
-      <c r="AI9" s="21"/>
-      <c r="AJ9" s="21"/>
-      <c r="AK9" s="21"/>
-      <c r="AL9" s="21"/>
-      <c r="AM9" s="21"/>
-      <c r="AN9" s="21"/>
-      <c r="AO9" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="AR9" s="21"/>
-      <c r="AS9" s="21"/>
-      <c r="AT9" s="21"/>
-      <c r="AU9" s="24"/>
-    </row>
-    <row r="10" spans="2:47" s="4" customFormat="1" ht="26.4" customHeight="1" thickBot="1">
-      <c r="B10" s="16"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
-      <c r="AH10" s="22"/>
-      <c r="AI10" s="22"/>
-      <c r="AJ10" s="22"/>
-      <c r="AK10" s="22"/>
-      <c r="AL10" s="22"/>
-      <c r="AM10" s="22"/>
-      <c r="AN10" s="22"/>
-      <c r="AO10" s="22"/>
-      <c r="AP10" s="22"/>
-      <c r="AQ10" s="22"/>
-      <c r="AR10" s="22"/>
-      <c r="AS10" s="22"/>
-      <c r="AT10" s="22"/>
-      <c r="AU10" s="25"/>
-    </row>
-    <row r="11" spans="2:47" hidden="1"/>
-    <row r="12" spans="2:47">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="13"/>
-      <c r="AK12" s="13"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="13"/>
-      <c r="AO12" s="13"/>
-      <c r="AP12" s="13"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="13"/>
-      <c r="AS12" s="13"/>
-      <c r="AT12" s="13"/>
-      <c r="AU12" s="13"/>
-    </row>
-    <row r="15" spans="2:47">
-      <c r="C15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="2:47">
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="4:12">
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="4:12">
-      <c r="D18" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="L18" s="26"/>
-    </row>
-    <row r="19" spans="4:12">
-      <c r="D19" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="27"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="12"/>
+      <c r="AA14" s="12"/>
+      <c r="AB14" s="12"/>
+      <c r="AC14" s="12"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="27"/>
+      <c r="AG14" s="14"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="AR8:AR10"/>
-    <mergeCell ref="AK8:AK10"/>
-    <mergeCell ref="AL8:AL10"/>
-    <mergeCell ref="AM8:AM10"/>
-    <mergeCell ref="AN8:AN10"/>
-    <mergeCell ref="AG8:AG10"/>
-    <mergeCell ref="AH8:AH10"/>
-    <mergeCell ref="AI8:AI10"/>
-    <mergeCell ref="AJ8:AJ10"/>
-    <mergeCell ref="Z8:Z10"/>
-    <mergeCell ref="AB8:AB10"/>
-    <mergeCell ref="AC8:AC10"/>
-    <mergeCell ref="AS8:AS10"/>
-    <mergeCell ref="AT8:AT10"/>
-    <mergeCell ref="AU8:AU10"/>
-    <mergeCell ref="AO9:AO10"/>
-    <mergeCell ref="AP9:AP10"/>
-    <mergeCell ref="AQ9:AQ10"/>
-    <mergeCell ref="AO8:AQ8"/>
-    <mergeCell ref="AD8:AD10"/>
-    <mergeCell ref="AE8:AE10"/>
-    <mergeCell ref="AF8:AF10"/>
-    <mergeCell ref="W8:W10"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="X8:X10"/>
-    <mergeCell ref="Y8:Y10"/>
-    <mergeCell ref="AA8:AA10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="P8:V8"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="C9:C10"/>
+  <mergeCells count="48">
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="G12:O12"/>
+    <mergeCell ref="P12:V12"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="AD12:AD14"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="AF12:AF14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AS12:AS14"/>
+    <mergeCell ref="AT12:AT14"/>
+    <mergeCell ref="AU12:AU14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AR12:AR14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AG12:AG14"/>
+    <mergeCell ref="AH12:AH14"/>
+    <mergeCell ref="AI12:AI14"/>
+    <mergeCell ref="AJ12:AJ14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1363,6 +1253,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFE98289BC91294F829EFFD4DC549C76" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19972903a613892b44bc7de177b9930c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="24f70235-d7ab-48ae-872a-f5e45d821dca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="851bba6bbcd0ff4aaccc95eb8de2c74d" ns3:_="">
     <xsd:import namespace="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
@@ -1512,12 +1408,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
@@ -1527,6 +1417,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E727EF53-D248-4693-8734-5FECE57054A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1542,20 +1448,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_04_08/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{FD76107A-A50E-4211-B2F4-EE95EDB93CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7346B3-CA4B-4113-BA38-32B7620E4FF6}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{FD76107A-A50E-4211-B2F4-EE95EDB93CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB0E25B9-CE71-45EE-90E4-A8FF04D8EC1B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -127,9 +127,6 @@
 Location</t>
   </si>
   <si>
-    <t>PAR / ARE / MR</t>
-  </si>
-  <si>
     <t>Number</t>
   </si>
   <si>
@@ -238,6 +235,9 @@
     <t>Old
 Amounts
 (in RPCPPE)</t>
+  </si>
+  <si>
+    <t>PAR / ICS / ARE / MR / RPCPPE</t>
   </si>
 </sst>
 </file>
@@ -483,58 +483,58 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,10 +553,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -876,16 +872,16 @@
     <col min="22" max="22" width="13.21875" style="3" customWidth="1"/>
     <col min="23" max="23" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.88671875" style="3"/>
-    <col min="25" max="25" width="10.5546875" style="24" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" style="12" customWidth="1"/>
     <col min="26" max="26" width="11.44140625" style="3" customWidth="1"/>
     <col min="27" max="28" width="8.88671875" style="3"/>
     <col min="29" max="29" width="13" style="3" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" style="24" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" style="24" customWidth="1"/>
-    <col min="32" max="32" width="12.21875" style="24" customWidth="1"/>
+    <col min="30" max="30" width="11.44140625" style="12" customWidth="1"/>
+    <col min="31" max="31" width="12.109375" style="12" customWidth="1"/>
+    <col min="32" max="32" width="12.21875" style="12" customWidth="1"/>
     <col min="33" max="33" width="11.6640625" style="3" customWidth="1"/>
     <col min="34" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="10.88671875" style="24" customWidth="1"/>
+    <col min="36" max="36" width="10.88671875" style="12" customWidth="1"/>
     <col min="37" max="38" width="8.88671875" style="3"/>
     <col min="39" max="39" width="13.6640625" style="3" customWidth="1"/>
     <col min="40" max="41" width="8.88671875" style="3"/>
@@ -899,21 +895,21 @@
   <sheetData>
     <row r="2" spans="2:47" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
-      <c r="Y2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AJ2" s="22"/>
+      <c r="Y2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AJ2" s="10"/>
     </row>
     <row r="3" spans="2:47" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y3" s="23"/>
-      <c r="AD3" s="23"/>
-      <c r="AE3" s="23"/>
-      <c r="AF3" s="23"/>
-      <c r="AJ3" s="23"/>
+        <v>50</v>
+      </c>
+      <c r="Y3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AJ3" s="11"/>
     </row>
     <row r="4" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
@@ -929,7 +925,7 @@
     </row>
     <row r="8" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="9"/>
     </row>
@@ -943,250 +939,250 @@
     </row>
     <row r="11" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="2:47" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="21"/>
+      <c r="E12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="10" t="s">
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="X12" s="10" t="s">
+      <c r="X12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="25" t="s">
+      <c r="Y12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z12" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ12" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="Z12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE12" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF12" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="AO12" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP12" s="15"/>
-      <c r="AQ12" s="15"/>
-      <c r="AR12" s="10" t="s">
+      <c r="AP12" s="21"/>
+      <c r="AQ12" s="21"/>
+      <c r="AR12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AS12" s="15" t="s">
+      <c r="AT12" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AT12" s="15" t="s">
+      <c r="AU12" s="22" t="s">
         <v>29</v>
-      </c>
-      <c r="AU12" s="16" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:47" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="20"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="13" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="I13" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="13" t="s">
+      <c r="M13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="N13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="P13" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="R13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="R13" s="13" t="s">
+      <c r="S13" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="S13" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="T13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="11"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="11"/>
-      <c r="AL13" s="11"/>
-      <c r="AM13" s="11"/>
-      <c r="AN13" s="11"/>
-      <c r="AO13" s="11" t="s">
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
+      <c r="AO13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AP13" s="13" t="s">
+      <c r="AQ13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="AQ13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="AR13" s="11"/>
-      <c r="AS13" s="11"/>
-      <c r="AT13" s="11"/>
-      <c r="AU13" s="17"/>
+      <c r="AR13" s="14"/>
+      <c r="AS13" s="14"/>
+      <c r="AT13" s="14"/>
+      <c r="AU13" s="23"/>
     </row>
     <row r="14" spans="2:47" s="4" customFormat="1" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="21"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
       <c r="T14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U14" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="V14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="27"/>
-      <c r="AG14" s="14"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="29"/>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="12"/>
-      <c r="AN14" s="12"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="12"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="12"/>
-      <c r="AU14" s="18"/>
+        <v>46</v>
+      </c>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="20"/>
+      <c r="AK14" s="15"/>
+      <c r="AL14" s="15"/>
+      <c r="AM14" s="15"/>
+      <c r="AN14" s="15"/>
+      <c r="AO14" s="15"/>
+      <c r="AP14" s="15"/>
+      <c r="AQ14" s="15"/>
+      <c r="AR14" s="15"/>
+      <c r="AS14" s="15"/>
+      <c r="AT14" s="15"/>
+      <c r="AU14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="48">

--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -5,16 +5,161 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_04_08/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{FD76107A-A50E-4211-B2F4-EE95EDB93CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB0E25B9-CE71-45EE-90E4-A8FF04D8EC1B}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F7B109-9EEC-4B10-855A-6F9FAEB3C1D2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="a">#REF!</definedName>
+    <definedName name="Account">#REF!</definedName>
+    <definedName name="Account1">#REF!</definedName>
+    <definedName name="Account2">#REF!</definedName>
+    <definedName name="Account3">#REF!</definedName>
+    <definedName name="AirconditioningUnits">#REF!</definedName>
+    <definedName name="Banca">#REF!</definedName>
+    <definedName name="Books">#REF!</definedName>
+    <definedName name="BuildingComponents">#REF!</definedName>
+    <definedName name="Buildings">#REF!</definedName>
+    <definedName name="Bulldozer">#REF!</definedName>
+    <definedName name="Calendar10Month">#REF!</definedName>
+    <definedName name="Calendar10MonthOption">MATCH(Calendar10Month,Months,0)</definedName>
+    <definedName name="Calendar10Year">#REF!</definedName>
+    <definedName name="Calendar11Month">#REF!</definedName>
+    <definedName name="Calendar11MonthOption">MATCH(Calendar11Month,Months,0)</definedName>
+    <definedName name="Calendar11Year">#REF!</definedName>
+    <definedName name="Calendar12Month">#REF!</definedName>
+    <definedName name="Calendar12MonthOption">MATCH(Calendar12Month,Months,0)</definedName>
+    <definedName name="Calendar12Year">#REF!</definedName>
+    <definedName name="Calendar1Month">#REF!</definedName>
+    <definedName name="Calendar1MonthOption">MATCH(Calendar1Month,Months,0)</definedName>
+    <definedName name="Calendar1Year">#REF!</definedName>
+    <definedName name="Calendar2Month">#REF!</definedName>
+    <definedName name="Calendar2MonthOption">MATCH(Calendar2Month,Months,0)</definedName>
+    <definedName name="Calendar2Year">#REF!</definedName>
+    <definedName name="Calendar3Month">#REF!</definedName>
+    <definedName name="Calendar3MonthOption">MATCH(Calendar3Month,Months,0)</definedName>
+    <definedName name="Calendar3Year">#REF!</definedName>
+    <definedName name="Calendar4Month">#REF!</definedName>
+    <definedName name="Calendar4MonthOption">MATCH(Calendar4Month,Months,0)</definedName>
+    <definedName name="Calendar4Year">#REF!</definedName>
+    <definedName name="Calendar5Month">#REF!</definedName>
+    <definedName name="Calendar5MonthOption">MATCH(Calendar5Month,Months,0)</definedName>
+    <definedName name="Calendar5Year">#REF!</definedName>
+    <definedName name="Calendar6Month">#REF!</definedName>
+    <definedName name="Calendar6MonthOption">MATCH(Calendar6Month,Months,0)</definedName>
+    <definedName name="Calendar6Year">#REF!</definedName>
+    <definedName name="Calendar7Month">#REF!</definedName>
+    <definedName name="Calendar7MonthOption">MATCH(Calendar7Month,Months,0)</definedName>
+    <definedName name="Calendar7Year">#REF!</definedName>
+    <definedName name="Calendar8Month">#REF!</definedName>
+    <definedName name="Calendar8MonthOption">MATCH(Calendar8Month,Months,0)</definedName>
+    <definedName name="Calendar8Year">#REF!</definedName>
+    <definedName name="Calendar9Month">#REF!</definedName>
+    <definedName name="Calendar9MonthOption">MATCH(Calendar9Month,Months,0)</definedName>
+    <definedName name="Calendar9Year">#REF!</definedName>
+    <definedName name="Car">#REF!</definedName>
+    <definedName name="ClosedCircuitTelevision">#REF!</definedName>
+    <definedName name="CommunicationEquipment">#REF!</definedName>
+    <definedName name="CommunicationsNetwork">#REF!</definedName>
+    <definedName name="Compactor">#REF!</definedName>
+    <definedName name="ComputerDesktopSet">#REF!</definedName>
+    <definedName name="Condition">#REF!</definedName>
+    <definedName name="Condition1">#REF!</definedName>
+    <definedName name="Condition2">#REF!</definedName>
+    <definedName name="Condition3">#REF!</definedName>
+    <definedName name="ConstructionandHeavyEquipment">#REF!</definedName>
+    <definedName name="DataCommunicationsEquipment">#REF!</definedName>
+    <definedName name="Days">{0,1,2,3,4,5,6}</definedName>
+    <definedName name="DiagnosticEquipment">#REF!</definedName>
+    <definedName name="DisasterResponseandRescue">#REF!</definedName>
+    <definedName name="Drones">#REF!</definedName>
+    <definedName name="Dropside">#REF!</definedName>
+    <definedName name="DumpTruck">#REF!</definedName>
+    <definedName name="Duplicating\PhotocopyingMachines">#REF!</definedName>
+    <definedName name="EarthquakeRescueEquipment">#REF!</definedName>
+    <definedName name="FirefightingEquipmentandAccessories">#REF!</definedName>
+    <definedName name="FloodControlSystems">#REF!</definedName>
+    <definedName name="FloodRescueEquipment">#REF!</definedName>
+    <definedName name="Forklift">#REF!</definedName>
+    <definedName name="Furniture\Fixtures\Books">#REF!</definedName>
+    <definedName name="FurnitureandFixtures">#REF!</definedName>
+    <definedName name="Guns">#REF!</definedName>
+    <definedName name="HighwaysandBridges">#REF!</definedName>
+    <definedName name="HospitalandHealthCenters">#REF!</definedName>
+    <definedName name="HospitalBeds">#REF!</definedName>
+    <definedName name="InformationandCommunicationTechnology">#REF!</definedName>
+    <definedName name="IrrigationCanalsandLaterals">#REF!</definedName>
+    <definedName name="LandslideRescueEquipment">#REF!</definedName>
+    <definedName name="Laptop">#REF!</definedName>
+    <definedName name="LifeSupport">#REF!</definedName>
+    <definedName name="Markets">#REF!</definedName>
+    <definedName name="MedicalEquipment">#REF!</definedName>
+    <definedName name="MedicalFurniture">#REF!</definedName>
+    <definedName name="MedicineTrolleys">#REF!</definedName>
+    <definedName name="MobileCar">#REF!</definedName>
+    <definedName name="MobileClinic">#REF!</definedName>
+    <definedName name="ModeofAcquisition">#REF!</definedName>
+    <definedName name="ModeofAcquisition1">#REF!</definedName>
+    <definedName name="Monitors">#REF!</definedName>
+    <definedName name="Months">{"January","February","March","April","May","June","July","August","September","October","November","December"}</definedName>
+    <definedName name="Motorboat">#REF!</definedName>
+    <definedName name="Motorcycle">#REF!</definedName>
+    <definedName name="MotorVehicles">#REF!</definedName>
+    <definedName name="OfficeEquipment">#REF!</definedName>
+    <definedName name="OtheMedicalEquipment">#REF!</definedName>
+    <definedName name="OtherCommunication\TelecommunicationFacilities">#REF!</definedName>
+    <definedName name="OtherCommunicationEquipment">#REF!</definedName>
+    <definedName name="OtherDisasterResponseandRescue">#REF!</definedName>
+    <definedName name="OtherFloodControlSystemFacilities">#REF!</definedName>
+    <definedName name="OtherFurnitureFixturesandBooks">#REF!</definedName>
+    <definedName name="OtherICTEquipment">#REF!</definedName>
+    <definedName name="OtherInfrastructureAssets\Components">#REF!</definedName>
+    <definedName name="OtherMachineryEquipment">#REF!</definedName>
+    <definedName name="OtherOfficeEquipment">#REF!</definedName>
+    <definedName name="OtherPoliceandSecurityEquipment">#REF!</definedName>
+    <definedName name="OtherRoadNetworkFacilities">#REF!</definedName>
+    <definedName name="OtherStructures">#REF!</definedName>
+    <definedName name="OtherTransportationEquipment">#REF!</definedName>
+    <definedName name="Parks\Plazas\Monuments">#REF!</definedName>
+    <definedName name="PeripheralsandAuxiliaryEquipmentnecessarytoputthesystemintooperationalmode">#REF!</definedName>
+    <definedName name="PoliceandSecurityEquipment">#REF!</definedName>
+    <definedName name="PoliceEquipment">#REF!</definedName>
+    <definedName name="PreLoadedSoftwareOperatingSystemsincludedinthecostofthecomputerhardware">#REF!</definedName>
+    <definedName name="Printers">#REF!</definedName>
+    <definedName name="Radio">#REF!</definedName>
+    <definedName name="RiverWalls">#REF!</definedName>
+    <definedName name="RoadNetworks">#REF!</definedName>
+    <definedName name="Roads">#REF!</definedName>
+    <definedName name="Scanners">#REF!</definedName>
+    <definedName name="SchoolBuildings">#REF!</definedName>
+    <definedName name="Seawalls">#REF!</definedName>
+    <definedName name="SecurityCameras">#REF!</definedName>
+    <definedName name="Slaughterhouses">#REF!</definedName>
+    <definedName name="SpecializedEquipments">#REF!</definedName>
+    <definedName name="SurveyEquipments">#REF!</definedName>
+    <definedName name="TechnicalandScientificEquipment">#REF!</definedName>
+    <definedName name="TherapeuticEquipment">#REF!</definedName>
+    <definedName name="Towers">#REF!</definedName>
+    <definedName name="Transceivers">#REF!</definedName>
+    <definedName name="Transmitters">#REF!</definedName>
+    <definedName name="Truck">#REF!</definedName>
+    <definedName name="VolcanicEruptionRescueEquipment">#REF!</definedName>
+    <definedName name="WasteTreatmentPlants">#REF!</definedName>
+    <definedName name="Watercrafts">#REF!</definedName>
+    <definedName name="WaterSourceFacility">#REF!</definedName>
+    <definedName name="WaterSupplySystems">#REF!</definedName>
+    <definedName name="WaterTreatmentPlants">#REF!</definedName>
+    <definedName name="WeekdayOption">MATCH(WeekStart,Weekdays,0)+10</definedName>
+    <definedName name="Weekdays">{"Monday","Tuesday","Wednesday","Thursday","Friday","Saturday","Sunday"}</definedName>
+    <definedName name="WeekStart">#REF!</definedName>
+    <definedName name="WeekStartValue">IF(WeekStart="Monday",2,1)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,6 +181,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
+    <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
+  </si>
+  <si>
     <t>Custodian 
 Item 
 Number</t>
@@ -226,27 +374,41 @@
 Number</t>
   </si>
   <si>
-    <t>Department:</t>
-  </si>
-  <si>
-    <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
-  </si>
-  <si>
     <t>Old
 Amounts
 (in RPCPPE)</t>
   </si>
   <si>
-    <t>PAR / ICS / ARE / MR / RPCPPE</t>
+    <t>PAR / ICS / ARE / MR /RPCPPE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Department:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -288,13 +450,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -460,14 +623,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -475,71 +635,77 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -553,6 +719,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -852,346 +1022,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C18FA19-E183-4684-9A16-B0E4B19C4ED4}">
-  <dimension ref="B2:AU14"/>
+  <dimension ref="B1:AU14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="8.88671875" style="3"/>
-    <col min="10" max="10" width="7.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="3"/>
-    <col min="13" max="13" width="16" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="3"/>
-    <col min="15" max="15" width="5.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.88671875" style="3"/>
-    <col min="20" max="20" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.21875" style="3" customWidth="1"/>
-    <col min="23" max="23" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.88671875" style="3"/>
-    <col min="25" max="25" width="10.5546875" style="12" customWidth="1"/>
-    <col min="26" max="26" width="11.44140625" style="3" customWidth="1"/>
-    <col min="27" max="28" width="8.88671875" style="3"/>
-    <col min="29" max="29" width="13" style="3" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" style="12" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" style="12" customWidth="1"/>
-    <col min="32" max="32" width="12.21875" style="12" customWidth="1"/>
-    <col min="33" max="33" width="11.6640625" style="3" customWidth="1"/>
-    <col min="34" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="10.88671875" style="12" customWidth="1"/>
-    <col min="37" max="38" width="8.88671875" style="3"/>
-    <col min="39" max="39" width="13.6640625" style="3" customWidth="1"/>
-    <col min="40" max="41" width="8.88671875" style="3"/>
-    <col min="42" max="42" width="11.5546875" style="3" customWidth="1"/>
-    <col min="43" max="43" width="8.88671875" style="3"/>
-    <col min="44" max="44" width="19.109375" style="3" customWidth="1"/>
-    <col min="45" max="45" width="6.5546875" style="3" customWidth="1"/>
-    <col min="46" max="46" width="9.33203125" style="3" customWidth="1"/>
-    <col min="47" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="2.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="5"/>
+    <col min="6" max="6" width="26.109375" style="14" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="14"/>
+    <col min="10" max="10" width="7.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="14"/>
+    <col min="13" max="13" width="16" style="14" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="14"/>
+    <col min="15" max="15" width="5.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="8.88671875" style="14"/>
+    <col min="20" max="20" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" style="14"/>
+    <col min="25" max="25" width="10.5546875" style="6" customWidth="1"/>
+    <col min="26" max="26" width="10.88671875" style="14" customWidth="1"/>
+    <col min="27" max="27" width="8.88671875" style="5"/>
+    <col min="28" max="28" width="8.88671875" style="14"/>
+    <col min="29" max="29" width="13.6640625" style="5" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" style="6"/>
+    <col min="31" max="31" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" style="6" customWidth="1"/>
+    <col min="33" max="33" width="11.33203125" style="14" customWidth="1"/>
+    <col min="34" max="35" width="8.88671875" style="5"/>
+    <col min="36" max="36" width="8.88671875" style="6"/>
+    <col min="37" max="37" width="8.88671875" style="14"/>
+    <col min="38" max="38" width="8.88671875" style="5"/>
+    <col min="39" max="41" width="8.88671875" style="14"/>
+    <col min="42" max="42" width="11.5546875" style="14" customWidth="1"/>
+    <col min="43" max="43" width="8.88671875" style="14"/>
+    <col min="44" max="44" width="19.109375" style="14" customWidth="1"/>
+    <col min="45" max="45" width="6.5546875" style="5" customWidth="1"/>
+    <col min="46" max="46" width="9.33203125" style="14" customWidth="1"/>
+    <col min="47" max="47" width="23.44140625" style="14" customWidth="1"/>
+    <col min="48" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:47" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:47" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
-      <c r="Y2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AJ2" s="10"/>
     </row>
-    <row r="3" spans="2:47" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="2:47" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="10"/>
+    </row>
+    <row r="5" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="10"/>
+    </row>
+    <row r="6" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="11"/>
+    </row>
+    <row r="7" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="15"/>
+    </row>
+    <row r="9" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="11"/>
+    </row>
+    <row r="11" spans="2:47" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="12"/>
+    </row>
+    <row r="12" spans="2:47" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AJ3" s="11"/>
+      <c r="Z12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP12" s="19"/>
+      <c r="AQ12" s="19"/>
+      <c r="AR12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS12" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU12" s="24" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
+    <row r="13" spans="2:47" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
+      <c r="C13" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="P13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="S13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="22"/>
+      <c r="AK13" s="22"/>
+      <c r="AL13" s="22"/>
+      <c r="AM13" s="22"/>
+      <c r="AN13" s="22"/>
+      <c r="AO13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR13" s="22"/>
+      <c r="AS13" s="20"/>
+      <c r="AT13" s="20"/>
+      <c r="AU13" s="25"/>
     </row>
-    <row r="5" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="9"/>
-    </row>
-    <row r="9" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-      <c r="C9" s="9"/>
-    </row>
-    <row r="10" spans="2:47" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="2:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="2:47" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="X12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z12" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE12" s="18" t="s">
+    <row r="14" spans="2:47" s="2" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="18"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AF12" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ12" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK12" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="AO12" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP12" s="21"/>
-      <c r="AQ12" s="21"/>
-      <c r="AR12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="AS12" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AT12" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="AU12" s="22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="2:47" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="28"/>
-      <c r="C13" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="R13" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="S13" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="25"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="25"/>
-      <c r="AF13" s="25"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="14"/>
-      <c r="AL13" s="14"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP13" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="AQ13" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="AR13" s="14"/>
-      <c r="AS13" s="14"/>
-      <c r="AT13" s="14"/>
-      <c r="AU13" s="23"/>
-    </row>
-    <row r="14" spans="2:47" s="4" customFormat="1" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="29"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="U14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="V14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="W14" s="15"/>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="26"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="26"/>
-      <c r="AF14" s="26"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="15"/>
-      <c r="AI14" s="15"/>
-      <c r="AJ14" s="20"/>
-      <c r="AK14" s="15"/>
-      <c r="AL14" s="15"/>
-      <c r="AM14" s="15"/>
-      <c r="AN14" s="15"/>
-      <c r="AO14" s="15"/>
-      <c r="AP14" s="15"/>
-      <c r="AQ14" s="15"/>
-      <c r="AR14" s="15"/>
-      <c r="AS14" s="15"/>
-      <c r="AT14" s="15"/>
-      <c r="AU14" s="24"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="23"/>
+      <c r="AJ14" s="23"/>
+      <c r="AK14" s="23"/>
+      <c r="AL14" s="23"/>
+      <c r="AM14" s="23"/>
+      <c r="AN14" s="23"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="23"/>
+      <c r="AQ14" s="23"/>
+      <c r="AR14" s="23"/>
+      <c r="AS14" s="21"/>
+      <c r="AT14" s="21"/>
+      <c r="AU14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="AR12:AR14"/>
+    <mergeCell ref="AS12:AS14"/>
+    <mergeCell ref="AT12:AT14"/>
+    <mergeCell ref="AU12:AU14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AI12:AI14"/>
+    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AG12:AG14"/>
+    <mergeCell ref="AH12:AH14"/>
+    <mergeCell ref="AD12:AD14"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="AF12:AF14"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="AA12:AA14"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="G12:O12"/>
     <mergeCell ref="P12:V12"/>
@@ -1207,33 +1393,12 @@
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="N13:N14"/>
-    <mergeCell ref="AD12:AD14"/>
-    <mergeCell ref="AE12:AE14"/>
-    <mergeCell ref="AF12:AF14"/>
-    <mergeCell ref="W12:W14"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="X12:X14"/>
-    <mergeCell ref="Y12:Y14"/>
-    <mergeCell ref="AA12:AA14"/>
-    <mergeCell ref="Z12:Z14"/>
-    <mergeCell ref="AB12:AB14"/>
-    <mergeCell ref="AC12:AC14"/>
-    <mergeCell ref="AS12:AS14"/>
-    <mergeCell ref="AT12:AT14"/>
-    <mergeCell ref="AU12:AU14"/>
-    <mergeCell ref="AO13:AO14"/>
-    <mergeCell ref="AP13:AP14"/>
-    <mergeCell ref="AQ13:AQ14"/>
-    <mergeCell ref="AO12:AQ12"/>
-    <mergeCell ref="AR12:AR14"/>
-    <mergeCell ref="AK12:AK14"/>
-    <mergeCell ref="AL12:AL14"/>
-    <mergeCell ref="AM12:AM14"/>
-    <mergeCell ref="AN12:AN14"/>
-    <mergeCell ref="AG12:AG14"/>
-    <mergeCell ref="AH12:AH14"/>
-    <mergeCell ref="AI12:AI14"/>
-    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1249,12 +1414,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFE98289BC91294F829EFFD4DC549C76" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19972903a613892b44bc7de177b9930c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="24f70235-d7ab-48ae-872a-f5e45d821dca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="851bba6bbcd0ff4aaccc95eb8de2c74d" ns3:_="">
     <xsd:import namespace="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
@@ -1404,6 +1563,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
@@ -1413,22 +1578,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E727EF53-D248-4693-8734-5FECE57054A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1444,4 +1593,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesAnnexTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Tempalte 2025_06_24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F7B109-9EEC-4B10-855A-6F9FAEB3C1D2}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9FA35BE-25F3-44A7-B510-B917C22D8022}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -409,7 +409,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,6 +467,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -623,10 +633,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -671,6 +682,30 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -680,32 +715,40 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -719,10 +762,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1037,29 +1076,34 @@
     <col min="12" max="12" width="8.88671875" style="14"/>
     <col min="13" max="13" width="16" style="14" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" style="14"/>
-    <col min="15" max="15" width="5.44140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.88671875" style="14"/>
+    <col min="15" max="15" width="13.33203125" style="14" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="14"/>
+    <col min="17" max="17" width="13.5546875" style="14" customWidth="1"/>
+    <col min="18" max="19" width="8.88671875" style="14"/>
     <col min="20" max="20" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" style="14" customWidth="1"/>
     <col min="22" max="22" width="10.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.88671875" style="14" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.88671875" style="14"/>
-    <col min="25" max="25" width="10.5546875" style="6" customWidth="1"/>
+    <col min="23" max="23" width="15.88671875" style="14" customWidth="1"/>
+    <col min="24" max="24" width="17.109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" style="34" customWidth="1"/>
     <col min="26" max="26" width="10.88671875" style="14" customWidth="1"/>
     <col min="27" max="27" width="8.88671875" style="5"/>
-    <col min="28" max="28" width="8.88671875" style="14"/>
+    <col min="28" max="28" width="13.6640625" style="14" customWidth="1"/>
     <col min="29" max="29" width="13.6640625" style="5" customWidth="1"/>
-    <col min="30" max="30" width="8.88671875" style="6"/>
-    <col min="31" max="31" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.44140625" style="6" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" style="34"/>
+    <col min="31" max="31" width="11.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" style="34" customWidth="1"/>
     <col min="33" max="33" width="11.33203125" style="14" customWidth="1"/>
-    <col min="34" max="35" width="8.88671875" style="5"/>
-    <col min="36" max="36" width="8.88671875" style="6"/>
+    <col min="34" max="34" width="8.88671875" style="37"/>
+    <col min="35" max="35" width="8.88671875" style="5"/>
+    <col min="36" max="36" width="8.88671875" style="34"/>
     <col min="37" max="37" width="8.88671875" style="14"/>
     <col min="38" max="38" width="8.88671875" style="5"/>
-    <col min="39" max="41" width="8.88671875" style="14"/>
-    <col min="42" max="42" width="11.5546875" style="14" customWidth="1"/>
-    <col min="43" max="43" width="8.88671875" style="14"/>
+    <col min="39" max="39" width="11.109375" style="14" customWidth="1"/>
+    <col min="40" max="40" width="17.21875" style="14" customWidth="1"/>
+    <col min="41" max="41" width="20.109375" style="14" customWidth="1"/>
+    <col min="42" max="42" width="21.109375" style="14" customWidth="1"/>
+    <col min="43" max="43" width="17" style="14" customWidth="1"/>
     <col min="44" max="44" width="19.109375" style="14" customWidth="1"/>
     <col min="45" max="45" width="6.5546875" style="5" customWidth="1"/>
     <col min="46" max="46" width="9.33203125" style="14" customWidth="1"/>
@@ -1067,253 +1111,320 @@
     <col min="48" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Y1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AJ1" s="27"/>
+    </row>
     <row r="2" spans="2:47" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
+      <c r="Y2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AJ2" s="28"/>
     </row>
     <row r="3" spans="2:47" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
+      <c r="Y3" s="29"/>
+      <c r="AD3" s="29"/>
+      <c r="AE3" s="29"/>
+      <c r="AF3" s="29"/>
+      <c r="AH3" s="29"/>
+      <c r="AJ3" s="29"/>
     </row>
     <row r="4" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="10"/>
+      <c r="Y4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AJ4" s="30"/>
     </row>
     <row r="5" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
+      <c r="Y5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AJ5" s="30"/>
     </row>
     <row r="6" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="11"/>
+      <c r="Y6" s="30"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AJ6" s="30"/>
     </row>
     <row r="7" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="11"/>
+      <c r="Y7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AJ7" s="30"/>
     </row>
     <row r="8" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C8" s="15"/>
+      <c r="Y8" s="30"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AJ8" s="30"/>
     </row>
     <row r="9" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
+      <c r="Y9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AJ9" s="30"/>
     </row>
     <row r="10" spans="2:47" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
+      <c r="Y10" s="30"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AJ10" s="30"/>
     </row>
     <row r="11" spans="2:47" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="12"/>
+      <c r="Y11" s="30"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AJ11" s="30"/>
     </row>
     <row r="12" spans="2:47" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19" t="s">
+      <c r="D12" s="16"/>
+      <c r="E12" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19" t="s">
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19" t="s">
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="X12" s="19" t="s">
+      <c r="X12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="Y12" s="19" t="s">
+      <c r="Y12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="Z12" s="19" t="s">
+      <c r="Z12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="AA12" s="19" t="s">
+      <c r="AA12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="AB12" s="19" t="s">
+      <c r="AB12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AC12" s="19" t="s">
+      <c r="AC12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AD12" s="19" t="s">
+      <c r="AD12" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="AE12" s="19" t="s">
+      <c r="AE12" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="AF12" s="19" t="s">
+      <c r="AF12" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="AG12" s="19" t="s">
+      <c r="AG12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AH12" s="19" t="s">
+      <c r="AH12" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="AI12" s="19" t="s">
+      <c r="AI12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AJ12" s="19" t="s">
+      <c r="AJ12" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="AK12" s="19" t="s">
+      <c r="AK12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AL12" s="19" t="s">
+      <c r="AL12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AM12" s="19" t="s">
+      <c r="AM12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AN12" s="19" t="s">
+      <c r="AN12" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="AO12" s="19" t="s">
+      <c r="AO12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="AP12" s="19"/>
-      <c r="AQ12" s="19"/>
-      <c r="AR12" s="19" t="s">
+      <c r="AP12" s="16"/>
+      <c r="AQ12" s="16"/>
+      <c r="AR12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AS12" s="19" t="s">
+      <c r="AS12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AT12" s="19" t="s">
+      <c r="AT12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AU12" s="24" t="s">
+      <c r="AU12" s="21" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:47" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="17"/>
-      <c r="C13" s="20" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="20" t="s">
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L13" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M13" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="O13" s="20" t="s">
+      <c r="O13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="P13" s="20" t="s">
+      <c r="P13" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="Q13" s="20" t="s">
+      <c r="Q13" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="R13" s="20" t="s">
+      <c r="R13" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="S13" s="20" t="s">
+      <c r="S13" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="T13" s="20" t="s">
+      <c r="T13" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="20"/>
-      <c r="AF13" s="20"/>
-      <c r="AG13" s="20"/>
-      <c r="AH13" s="22"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="22"/>
-      <c r="AK13" s="22"/>
-      <c r="AL13" s="22"/>
-      <c r="AM13" s="22"/>
-      <c r="AN13" s="22"/>
-      <c r="AO13" s="20" t="s">
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="35"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="35"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="AP13" s="20" t="s">
+      <c r="AP13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="AQ13" s="20" t="s">
+      <c r="AQ13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="AR13" s="22"/>
-      <c r="AS13" s="20"/>
-      <c r="AT13" s="20"/>
-      <c r="AU13" s="25"/>
+      <c r="AR13" s="17"/>
+      <c r="AS13" s="19"/>
+      <c r="AT13" s="19"/>
+      <c r="AU13" s="22"/>
     </row>
     <row r="14" spans="2:47" s="2" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="18"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
       <c r="T14" s="3" t="s">
         <v>44</v>
       </c>
@@ -1323,61 +1434,40 @@
       <c r="V14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="23"/>
-      <c r="AI14" s="23"/>
-      <c r="AJ14" s="23"/>
-      <c r="AK14" s="23"/>
-      <c r="AL14" s="23"/>
-      <c r="AM14" s="23"/>
-      <c r="AN14" s="23"/>
-      <c r="AO14" s="21"/>
-      <c r="AP14" s="23"/>
-      <c r="AQ14" s="23"/>
-      <c r="AR14" s="23"/>
-      <c r="AS14" s="21"/>
-      <c r="AT14" s="21"/>
-      <c r="AU14" s="26"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="18"/>
+      <c r="Y14" s="33"/>
+      <c r="Z14" s="18"/>
+      <c r="AA14" s="18"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="20"/>
+      <c r="AH14" s="36"/>
+      <c r="AI14" s="18"/>
+      <c r="AJ14" s="36"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="18"/>
+      <c r="AM14" s="18"/>
+      <c r="AN14" s="18"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="18"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="18"/>
+      <c r="AS14" s="20"/>
+      <c r="AT14" s="20"/>
+      <c r="AU14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="AR12:AR14"/>
-    <mergeCell ref="AS12:AS14"/>
-    <mergeCell ref="AT12:AT14"/>
-    <mergeCell ref="AU12:AU14"/>
-    <mergeCell ref="AO13:AO14"/>
-    <mergeCell ref="AP13:AP14"/>
-    <mergeCell ref="AQ13:AQ14"/>
-    <mergeCell ref="AC12:AC14"/>
-    <mergeCell ref="AN12:AN14"/>
-    <mergeCell ref="AO12:AQ12"/>
-    <mergeCell ref="AI12:AI14"/>
-    <mergeCell ref="AJ12:AJ14"/>
-    <mergeCell ref="AK12:AK14"/>
-    <mergeCell ref="AG12:AG14"/>
-    <mergeCell ref="AH12:AH14"/>
-    <mergeCell ref="AD12:AD14"/>
-    <mergeCell ref="AE12:AE14"/>
-    <mergeCell ref="AF12:AF14"/>
-    <mergeCell ref="AL12:AL14"/>
-    <mergeCell ref="AM12:AM14"/>
-    <mergeCell ref="W12:W14"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="X12:X14"/>
-    <mergeCell ref="Y12:Y14"/>
-    <mergeCell ref="AB12:AB14"/>
-    <mergeCell ref="Z12:Z14"/>
-    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="G12:O12"/>
     <mergeCell ref="P12:V12"/>
@@ -1393,24 +1483,42 @@
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="N13:N14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AI12:AI14"/>
+    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AG12:AG14"/>
+    <mergeCell ref="AH12:AH14"/>
+    <mergeCell ref="AD12:AD14"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="AF12:AF14"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AR12:AR14"/>
+    <mergeCell ref="AS12:AS14"/>
+    <mergeCell ref="AT12:AT14"/>
+    <mergeCell ref="AU12:AU14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AQ13:AQ14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1564,15 +1672,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1596,17 +1715,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>